--- a/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1985001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1985001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1985001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,11 +1610,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1985001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1632,11 +1712,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1985001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1714,11 +1814,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1985001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>1985001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>1985001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>1985001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>1985001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>1985001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>1985001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1916,31 +1916,83 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -1966,31 +2018,83 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -2016,31 +2120,83 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
@@ -2066,31 +2222,83 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
@@ -2116,31 +2324,83 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
@@ -2166,31 +2426,83 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>1985002</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
@@ -2216,31 +2528,83 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
@@ -2266,31 +2630,83 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
@@ -2316,31 +2732,83 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
@@ -2366,31 +2834,83 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
@@ -2414,6 +2934,566 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>79</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1985003</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>29</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>99</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>99</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>79</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>999</v>
+      </c>
+      <c r="P28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>79</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1985004</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>

--- a/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1985_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV30"/>
+  <dimension ref="A1:AV22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1339,9 +1339,13 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>99</v>
@@ -1354,14 +1358,14 @@
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
       <c r="O7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R7" s="6" t="n"/>
@@ -1371,14 +1375,14 @@
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
       <c r="X7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA7" s="6" t="n"/>
@@ -1408,22 +1412,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1985001</t>
+          <t>1985002</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1985001</t>
+          <t>1985002</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1441,7 +1445,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>0</v>
       </c>
@@ -1456,14 +1464,14 @@
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
       <c r="O8" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R8" s="6" t="n"/>
@@ -1473,14 +1481,14 @@
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA8" s="6" t="n"/>
@@ -1510,22 +1518,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>1985001</t>
+          <t>1985003</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1985001</t>
+          <t>1985003</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1543,12 +1551,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -1558,14 +1570,14 @@
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
       <c r="O9" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R9" s="6" t="n"/>
@@ -1575,14 +1587,14 @@
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA9" s="6" t="n"/>
@@ -1612,22 +1624,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1985001</t>
+          <t>1985004</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1985001</t>
+          <t>1985004</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1645,7 +1657,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>0</v>
       </c>
@@ -1660,14 +1676,14 @@
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R10" s="6" t="n"/>
@@ -1677,14 +1693,14 @@
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA10" s="6" t="n"/>
@@ -1712,83 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1985001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1985001</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z11" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -1814,83 +1778,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1985001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>1985001</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y12" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
@@ -1916,83 +1828,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
+      <c r="Z13" s="6" t="n"/>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -2018,83 +1878,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -2120,83 +1928,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y15" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z15" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
@@ -2222,83 +1978,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y16" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z16" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
@@ -2324,83 +2028,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y17" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z17" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
@@ -2426,83 +2078,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>1985002</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(100세형)</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y18" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z18" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
@@ -2528,83 +2128,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y19" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z19" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
@@ -2630,83 +2178,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y20" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z20" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
       <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
@@ -2732,83 +2228,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y21" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z21" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
       <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
@@ -2834,83 +2278,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y22" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z22" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
       <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
@@ -2934,566 +2326,6 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>79</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>999</v>
-      </c>
-      <c r="P23" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X23" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1985003</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형)무배당(상해급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>29</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>999</v>
-      </c>
-      <c r="P24" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X24" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>99</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>999</v>
-      </c>
-      <c r="P25" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X25" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>99</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>999</v>
-      </c>
-      <c r="P26" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X26" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>79</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>999</v>
-      </c>
-      <c r="P27" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X27" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>29</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>999</v>
-      </c>
-      <c r="P28" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X28" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>79</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>999</v>
-      </c>
-      <c r="P29" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X29" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1985004</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 기본형 급여 실손의료비보장보험[계약전환용](갱신형) 무배당(질병급여형)(30세형)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>29</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>999</v>
-      </c>
-      <c r="P30" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X30" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>
